--- a/excel_data/Feedback.xlsx
+++ b/excel_data/Feedback.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -441,9 +441,223 @@
         <v>Test message</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Arpit Singh</v>
+      </c>
+      <c r="B4" t="str">
+        <v>arpitsin28@gmail.com</v>
+      </c>
+      <c r="C4" t="str">
+        <v>09473733115</v>
+      </c>
+      <c r="D4" t="str">
+        <v>jnhgf</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>prakash n gaikwad</v>
+      </c>
+      <c r="B5" t="str">
+        <v>gaikwadprakash27761@gmail.com</v>
+      </c>
+      <c r="C5" t="str">
+        <v>7211153627</v>
+      </c>
+      <c r="D5" t="str">
+        <v>seeking mapping services for major cities in india appro @ 200nos</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ncniIwbyvCCG</v>
+      </c>
+      <c r="B6" t="str">
+        <v>otudevimi12@gmail.com</v>
+      </c>
+      <c r="C6" t="str">
+        <v>3924656001</v>
+      </c>
+      <c r="D6" t="str">
+        <v>xyPucbBYJ</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Varun S l</v>
+      </c>
+      <c r="B7" t="str">
+        <v>varun@talkinglands.com</v>
+      </c>
+      <c r="C7" t="str">
+        <v>9483271440</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Need demo , We are a Proptech company looking for data</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">Joyston Francis Rodrigues </v>
+      </c>
+      <c r="B8" t="str">
+        <v>joystonrodrigues16@gmail.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>8296839379</v>
+      </c>
+      <c r="D8" t="str">
+        <v xml:space="preserve">As a final year experience student studying in Mangalore Karnataka, Can I get a internship in your Company </v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>VxNLiXEaWnZKBCIoanVTsH</v>
+      </c>
+      <c r="B9" t="str">
+        <v>mayateyoxap60@gmail.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>9666471538</v>
+      </c>
+      <c r="D9" t="str">
+        <v>XkFprJgOSQWZYYmQhnQV</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Alyssa Stone</v>
+      </c>
+      <c r="B10" t="str">
+        <v>alyssa@turbojot.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2158218810</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Hi! My name is Alyssa and I’d love to invite you to try TurboJot. I actually founded the company. It’s built to automate contact form submissions at scale. Simply upload a list of URLs and TurboJot automatically finds and submits contact forms on those sites. It beats cold email and paid ads on ROI and costs just $0.10 per submission. Powered by a rotating IP network, stealth browser, AI captcha solving, and human-like browsing behavior. You can sign up for free and give it a try here. I’d really appreciate the support! https://www.turbojot.com/</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Alyssa Stone</v>
+      </c>
+      <c r="B11" t="str">
+        <v>alyssa@turbojot.com</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2158218810</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Hi! My name is Alyssa and I’d love to invite you to try TurboJot. I actually founded the company. It’s built to automate contact form submissions at scale. Simply upload a list of URLs and TurboJot automatically finds and submits contact forms on those sites. It beats cold email and paid ads on ROI and costs just $0.10 per submission. Powered by a rotating IP network, stealth browser, AI captcha solving, and human-like browsing behavior. You can sign up for free and give it a try here. I’d really appreciate the support! https://www.turbojot.com/</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>Sahana J</v>
+      </c>
+      <c r="B12" t="str">
+        <v>sahanakhan220@gmail.com</v>
+      </c>
+      <c r="C12" t="str">
+        <v>7975292310</v>
+      </c>
+      <c r="D12" t="str" xml:space="preserve">
+        <v xml:space="preserve">I'm Sahana J 
+       I'm looking for a job if any vacancy is there then let me know </v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve">Sushant kharade </v>
+      </c>
+      <c r="B13" t="str">
+        <v>sushantkharade1112@gmail.com</v>
+      </c>
+      <c r="C13" t="str">
+        <v>9370125900</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Job</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">Sushat  Suresh kharade </v>
+      </c>
+      <c r="B14" t="str">
+        <v>sushantkharade1112@gmail.com</v>
+      </c>
+      <c r="C14" t="str">
+        <v>9370125900</v>
+      </c>
+      <c r="D14" t="str">
+        <v xml:space="preserve">Job gis executive </v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Sophie Lane</v>
+      </c>
+      <c r="B15" t="str">
+        <v>sophie@sendproud.com</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2155394452</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Hi, I’m Sophie! I tried to find you on LinkedIn but couldn’t, so I’m reaching out here. I help businesses book meetings, drive traffic, and generate user sign ups through targeted outreach using my extensive private network, built over 12+ years, with access to over 100 million contacts. We’ll have a quick call to set a clear goal for your business, and I’ll personally work to make sure we reach it. You choose the result you want, whether that’s booked meetings, website traffic, user sign ups, or another measurable outcome, and if I fall short by even one, I’ll refund your money in full. Schedule a time with me here: https://calendly.com/sendproud/30min</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Sophie Lane</v>
+      </c>
+      <c r="B16" t="str">
+        <v>sophie@sendproud.com</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2155394452</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Hi, I’m Sophie! I tried to find you on LinkedIn but couldn’t, so I’m reaching out here. I help businesses book meetings, drive traffic, and generate user sign ups through targeted outreach using my extensive private network, built over 12+ years, with access to over 100 million contacts. We’ll have a quick call to set a clear goal for your business, and I’ll personally work to make sure we reach it. You choose the result you want, whether that’s booked meetings, website traffic, user sign ups, or another measurable outcome, and if I fall short by even one, I’ll refund your money in full. Schedule a time with me here: https://calendly.com/sendproud/30min</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>Suvosree Roy</v>
+      </c>
+      <c r="B17" t="str">
+        <v>info@digitalindian.co.in</v>
+      </c>
+      <c r="C17" t="str">
+        <v>9030080679</v>
+      </c>
+      <c r="D17" t="str" xml:space="preserve">
+        <v xml:space="preserve">I hope this message finds you well.
+I am writing on behalf of DigitalIndian Business Solutions Pvt. Ltd., a growing technology and consulting firm specializing in Geographic Information Systems (GIS), data management, and IT-enabled services.
+With the GIS industry witnessing rapid growth in India, the demand for high-precision spatial data, mapping, and decision-support solutions continues to rise. We understand the critical importance of accuracy and reliability in GIS deliverables, particularly across sectors such as urban planning, transportation, infrastructure, utilities, environmental management, and e-governance.
+At Digital Indian Business Solutions, we take pride in consistently achieving over 80% accuracy in GIS data processing, feature extraction, mapping, and quality-controlled deliverables. This is supported by our robust quality assurance framework, experienced professionals, and the use of advanced GIS tools and technologies.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Pranita Bendre</v>
+      </c>
+      <c r="B18" t="str">
+        <v>pranitabendre@gmail.com</v>
+      </c>
+      <c r="C18" t="str">
+        <v>9762726070</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Hello, I hope you are doing well. I wanted to enquire if there are any current or upcoming job vacancies in your organization related to GIS field. I have 3 years of experience in GIS and HD maps and I am actively looking for new opportunities. Please let me know if there are any suitable openings. Thank you!</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
   </ignoredErrors>
 </worksheet>
 </file>